--- a/order_forms/002_car_rental_intake_form--order_forms.xlsx
+++ b/order_forms/002_car_rental_intake_form--order_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -877,8 +877,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="37" customWidth="1" min="2" max="2"/>
+    <col width="37" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -906,12 +906,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'economy_(small)',_'value':_'economy'}</t>
+          <t>economy_(small)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Economy (Small)', 'value': 'economy'}</t>
+          <t>Economy (Small)</t>
         </is>
       </c>
     </row>
@@ -923,12 +923,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'compact_(medium)',_'value':_'compact'}</t>
+          <t>compact_(medium)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Compact (Medium)', 'value': 'compact'}</t>
+          <t>Compact (Medium)</t>
         </is>
       </c>
     </row>
@@ -940,12 +940,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'suv_(large)',_'value':_'suv'}</t>
+          <t>suv_(large)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'SUV (Large)', 'value': 'suv'}</t>
+          <t>SUV (Large)</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'luxury',_'value':_'luxury'}</t>
+          <t>luxury</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Luxury', 'value': 'luxury'}</t>
+          <t>Luxury</t>
         </is>
       </c>
     </row>
@@ -974,12 +974,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'full_coverage_(standard)',_'value':_'full'}</t>
+          <t>full_coverage_(standard)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Full Coverage (Standard)', 'value': 'full'}</t>
+          <t>Full Coverage (Standard)</t>
         </is>
       </c>
     </row>
@@ -991,12 +991,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'basic_liability',_'value':_'basic'}</t>
+          <t>basic_liability</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Basic Liability', 'value': 'basic'}</t>
+          <t>Basic Liability</t>
         </is>
       </c>
     </row>
@@ -1008,12 +1008,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'decline_insurance_(personal_policy)',_'value':_'decline'}</t>
+          <t>decline_insurance_(personal_policy)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Decline Insurance (Personal Policy)', 'value': 'decline'}</t>
+          <t>Decline Insurance (Personal Policy)</t>
         </is>
       </c>
     </row>
@@ -1025,12 +1025,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'gps_navigation',_'value':_'gps'}</t>
+          <t>gps_navigation</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'GPS Navigation', 'value': 'gps'}</t>
+          <t>GPS Navigation</t>
         </is>
       </c>
     </row>
@@ -1042,12 +1042,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'child_safety_seat',_'value':_'car_seat'}</t>
+          <t>child_safety_seat</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Child Safety Seat', 'value': 'car_seat'}</t>
+          <t>Child Safety Seat</t>
         </is>
       </c>
     </row>
@@ -1059,12 +1059,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'roadside_assistance_kit',_'value':_'roadside'}</t>
+          <t>roadside_assistance_kit</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Roadside Assistance Kit', 'value': 'roadside'}</t>
+          <t>Roadside Assistance Kit</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'yes,_i_certify',_'value':_true}</t>
+          <t>yes,_i_certify</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Yes, I certify', 'value': True}</t>
+          <t>Yes, I certify</t>
         </is>
       </c>
     </row>
